--- a/event_feedback_forms/020_event_fee_structure_survey--event_feedback_forms.xlsx
+++ b/event_feedback_forms/020_event_fee_structure_survey--event_feedback_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Event Type</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional Fees</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -617,7 +617,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Additional Fees for</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,7 +630,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,7 +640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Clarity of Fee Structure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Recommend to Others</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Fair and Transparent</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,7 +699,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Time Frame for Ticket Sales and Event Preparation</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,7 +722,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,11 +732,57 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Comparison with Other Events</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Unexpected Fees</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_12</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Suggestions for Improvement</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -753,10 +799,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -786,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>base_price</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>base price</t>
         </is>
       </c>
     </row>
@@ -803,46 +849,46 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>price_per_attendee</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>price per attendee</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>event_fee_structure_survey_page_2_choices</t>
+          <t>event_fee_structure_survey_page_1_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price_per_item</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>base_price</t>
+          <t>price per item</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>event_fee_structure_survey_page_2_choices</t>
+          <t>event_fee_structure_survey_page_1_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>price_per_attendee</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>price_per_attendee</t>
+          <t>other</t>
         </is>
       </c>
     </row>
@@ -854,12 +900,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>price_per_item</t>
+          <t>revenue_per_event</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>price_per_item</t>
+          <t>revenue per event</t>
         </is>
       </c>
     </row>
@@ -871,12 +917,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>revenue_per_event</t>
+          <t>total_revenue</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>revenue_per_event</t>
+          <t>total revenue</t>
         </is>
       </c>
     </row>
@@ -888,12 +934,182 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>total_revenue</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>total_revenue</t>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_3_choices</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>concert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>concert</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_3_choices</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>festival</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>festival</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_3_choices</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>conference</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>conference</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_3_choices</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>very_clear</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>very clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>somewhat_clear</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>somewhat clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_6_choices</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>not_clear</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>not clear</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>unfair</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>unfair</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>event_fee_structure_survey_page_10_choices</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>neutral</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>neutral</t>
         </is>
       </c>
     </row>
